--- a/Datos Experimentales/Data 24027.xlsx
+++ b/Datos Experimentales/Data 24027.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A8E003-43DE-4BD4-8A97-3DEB85E1DD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1110,11 +1121,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1143,14 +1151,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1475,10 +1492,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B118"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1486,7 +1504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1494,7 +1512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1502,7 +1520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1510,7 +1528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1518,7 +1536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1526,7 +1544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1534,7 +1552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1542,7 +1560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1550,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1558,7 +1576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1566,7 +1584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1574,7 +1592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1582,7 +1600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1590,7 +1608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1598,7 +1616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1606,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1614,7 +1632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1622,7 +1640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1630,7 +1648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1638,7 +1656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1646,7 +1664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1654,7 +1672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1662,7 +1680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1670,7 +1688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1678,7 +1696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1686,7 +1704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1694,7 +1712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1702,7 +1720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1710,7 +1728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1718,7 +1736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1726,7 +1744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1734,7 +1752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1742,7 +1760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1750,7 +1768,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1758,7 +1776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1766,7 +1784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1774,7 +1792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1782,7 +1800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1790,7 +1808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1798,7 +1816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1806,7 +1824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1814,7 +1832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1822,7 +1840,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1830,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1838,7 +1856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1846,7 +1864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1854,7 +1872,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1862,7 +1880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1870,7 +1888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1878,7 +1896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1886,7 +1904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1894,7 +1912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1902,7 +1920,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1910,7 +1928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1918,7 +1936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1926,7 +1944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1934,7 +1952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1942,7 +1960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1950,7 +1968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1958,7 +1976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1966,7 +1984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1974,7 +1992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -1982,7 +2000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -1990,7 +2008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -1998,7 +2016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -2006,7 +2024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -2014,7 +2032,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -2022,7 +2040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -2030,7 +2048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -2038,7 +2056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -2046,7 +2064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -2054,7 +2072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -2062,7 +2080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2070,7 +2088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2078,7 +2096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2086,7 +2104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2094,7 +2112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2102,7 +2120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2110,7 +2128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -2118,7 +2136,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2126,7 +2144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2134,7 +2152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -2142,7 +2160,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2150,7 +2168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2158,7 +2176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2166,7 +2184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2174,7 +2192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2182,7 +2200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2190,7 +2208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2198,7 +2216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2206,7 +2224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2214,7 +2232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2222,7 +2240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2230,7 +2248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2238,7 +2256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2246,7 +2264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2254,7 +2272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>109</v>
       </c>
@@ -2262,7 +2280,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2270,7 +2288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2278,7 +2296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2286,7 +2304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2294,7 +2312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2302,7 +2320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2310,7 +2328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2318,7 +2336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2326,7 +2344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2334,7 +2352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2342,7 +2360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2350,7 +2368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2358,7 +2376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2366,7 +2384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2374,7 +2392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>125</v>
       </c>
@@ -2382,7 +2400,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2390,7 +2408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2398,7 +2416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2406,7 +2424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2414,7 +2432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>131</v>
       </c>
@@ -2423,27 +2441,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B118"/>
+    <ignoredError sqref="A1:B118" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -2464,17 +2486,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C78"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -2485,7 +2509,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>282</v>
       </c>
@@ -2496,7 +2520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>283</v>
       </c>
@@ -2507,29 +2531,29 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>284</v>
       </c>
       <c r="B4">
-        <v>0.7013888888888888</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>285</v>
       </c>
       <c r="B5">
-        <v>0.9513888888888888</v>
+        <v>0.95138888888888884</v>
       </c>
       <c r="C5">
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -2540,7 +2564,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -2551,7 +2575,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>288</v>
       </c>
@@ -2562,7 +2586,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>289</v>
       </c>
@@ -2573,777 +2597,779 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>290</v>
       </c>
       <c r="B10">
-        <v>2.201388888888889</v>
+        <v>2.2013888888888888</v>
       </c>
       <c r="C10">
         <v>13.5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>291</v>
       </c>
       <c r="B11">
-        <v>2.451388888888889</v>
+        <v>2.4513888888888888</v>
       </c>
       <c r="C11">
         <v>14</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>292</v>
       </c>
       <c r="B12">
-        <v>2.701388888888889</v>
+        <v>2.7013888888888888</v>
       </c>
       <c r="C12">
         <v>14</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>293</v>
       </c>
       <c r="B13">
-        <v>2.951388888888889</v>
+        <v>2.9513888888888888</v>
       </c>
       <c r="C13">
         <v>14</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>294</v>
       </c>
       <c r="B14">
-        <v>3.201388888888889</v>
+        <v>3.2013888888888888</v>
       </c>
       <c r="C14">
         <v>13.5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>295</v>
       </c>
       <c r="B15">
-        <v>3.451388888888889</v>
+        <v>3.4513888888888888</v>
       </c>
       <c r="C15">
         <v>13.4</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>296</v>
       </c>
       <c r="B16">
-        <v>3.701388888888889</v>
+        <v>3.7013888888888888</v>
       </c>
       <c r="C16">
         <v>14</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>297</v>
       </c>
       <c r="B17">
-        <v>3.951388888888889</v>
+        <v>3.9513888888888888</v>
       </c>
       <c r="C17">
         <v>14</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>298</v>
       </c>
       <c r="B18">
-        <v>4.201388888888889</v>
+        <v>4.2013888888888893</v>
       </c>
       <c r="C18">
         <v>13.4</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>299</v>
       </c>
       <c r="B19">
-        <v>4.451388888888889</v>
+        <v>4.4513888888888893</v>
       </c>
       <c r="C19">
         <v>14.1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>300</v>
       </c>
       <c r="B20">
-        <v>4.701388888888889</v>
+        <v>4.7013888888888893</v>
       </c>
       <c r="C20">
         <v>14</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>301</v>
       </c>
       <c r="B21">
-        <v>4.951388888888889</v>
+        <v>4.9513888888888893</v>
       </c>
       <c r="C21">
         <v>14</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>302</v>
       </c>
       <c r="B22">
-        <v>5.201388888888889</v>
+        <v>5.2013888888888893</v>
       </c>
       <c r="C22">
         <v>13.8</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>303</v>
       </c>
       <c r="B23">
-        <v>5.451388888888889</v>
+        <v>5.4513888888888893</v>
       </c>
       <c r="C23">
         <v>13.6</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>304</v>
       </c>
       <c r="B24">
-        <v>5.701388888888889</v>
+        <v>5.7013888888888893</v>
       </c>
       <c r="C24">
         <v>14</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>305</v>
       </c>
       <c r="B25">
-        <v>5.951388888888889</v>
+        <v>5.9513888888888893</v>
       </c>
       <c r="C25">
         <v>14</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>306</v>
       </c>
       <c r="B26">
-        <v>6.201388888888889</v>
+        <v>6.2013888888888893</v>
       </c>
       <c r="C26">
         <v>13.9</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>307</v>
       </c>
       <c r="B27">
-        <v>6.451388888888889</v>
+        <v>6.4513888888888893</v>
       </c>
       <c r="C27">
         <v>13.7</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>308</v>
       </c>
       <c r="B28">
-        <v>6.701388888888889</v>
+        <v>6.7013888888888893</v>
       </c>
       <c r="C28">
         <v>13.5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>309</v>
       </c>
       <c r="B29">
-        <v>6.951388888888889</v>
+        <v>6.9513888888888893</v>
       </c>
       <c r="C29">
         <v>14</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>310</v>
       </c>
       <c r="B30">
-        <v>7.201388888888889</v>
+        <v>7.2013888888888893</v>
       </c>
       <c r="C30">
         <v>14</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>311</v>
       </c>
       <c r="B31">
-        <v>7.451388888888889</v>
+        <v>7.4513888888888893</v>
       </c>
       <c r="C31">
         <v>13.8</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>312</v>
       </c>
       <c r="B32">
-        <v>7.701388888888889</v>
+        <v>7.7013888888888893</v>
       </c>
       <c r="C32">
         <v>14.5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>313</v>
       </c>
       <c r="B33">
-        <v>7.951388888888889</v>
+        <v>7.9513888888888893</v>
       </c>
       <c r="C33">
         <v>13.9</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>314</v>
       </c>
       <c r="B34">
-        <v>8.20138888888889</v>
+        <v>8.2013888888888893</v>
       </c>
       <c r="C34">
         <v>13.6</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>315</v>
       </c>
       <c r="B35">
-        <v>8.45138888888889</v>
+        <v>8.4513888888888893</v>
       </c>
       <c r="C35">
         <v>14</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>316</v>
       </c>
       <c r="B36">
-        <v>8.70138888888889</v>
+        <v>8.7013888888888893</v>
       </c>
       <c r="C36">
         <v>14.4</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>317</v>
       </c>
       <c r="B37">
-        <v>8.95138888888889</v>
+        <v>8.9513888888888893</v>
       </c>
       <c r="C37">
         <v>13.4</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>318</v>
       </c>
       <c r="B38">
-        <v>9.20138888888889</v>
+        <v>9.2013888888888893</v>
       </c>
       <c r="C38">
         <v>13.8</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>319</v>
       </c>
       <c r="B39">
-        <v>9.45138888888889</v>
+        <v>9.4513888888888893</v>
       </c>
       <c r="C39">
         <v>13.6</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>320</v>
       </c>
       <c r="B40">
-        <v>9.70138888888889</v>
+        <v>9.7013888888888893</v>
       </c>
       <c r="C40">
         <v>14.5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>321</v>
       </c>
       <c r="B41">
-        <v>9.95138888888889</v>
+        <v>9.9513888888888893</v>
       </c>
       <c r="C41">
         <v>13.6</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>322</v>
       </c>
       <c r="B42">
-        <v>10.20138888888889</v>
+        <v>10.201388888888889</v>
       </c>
       <c r="C42">
         <v>14</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>323</v>
       </c>
       <c r="B43">
-        <v>10.45138888888889</v>
+        <v>10.451388888888889</v>
       </c>
       <c r="C43">
         <v>14.1</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>324</v>
       </c>
       <c r="B44">
-        <v>10.70138888888889</v>
+        <v>10.701388888888889</v>
       </c>
       <c r="C44">
         <v>13.8</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>325</v>
       </c>
       <c r="B45">
-        <v>10.95138888888889</v>
+        <v>10.951388888888889</v>
       </c>
       <c r="C45">
         <v>14.1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>326</v>
       </c>
       <c r="B46">
-        <v>11.20138888888889</v>
+        <v>11.201388888888889</v>
       </c>
       <c r="C46">
         <v>14.3</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>327</v>
       </c>
       <c r="B47">
-        <v>11.45138888888889</v>
+        <v>11.451388888888889</v>
       </c>
       <c r="C47">
         <v>13.5</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>328</v>
       </c>
       <c r="B48">
-        <v>11.70138888888889</v>
+        <v>11.701388888888889</v>
       </c>
       <c r="C48">
         <v>14.5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>329</v>
       </c>
       <c r="B49">
-        <v>11.95138888888889</v>
+        <v>11.951388888888889</v>
       </c>
       <c r="C49">
         <v>13.9</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>330</v>
       </c>
       <c r="B50">
-        <v>12.20138888888889</v>
+        <v>12.201388888888889</v>
       </c>
       <c r="C50">
         <v>13.8</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>331</v>
       </c>
       <c r="B51">
-        <v>12.45138888888889</v>
+        <v>12.451388888888889</v>
       </c>
       <c r="C51">
         <v>14.5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>332</v>
       </c>
       <c r="B52">
-        <v>12.70138888888889</v>
+        <v>12.701388888888889</v>
       </c>
       <c r="C52">
         <v>13.7</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>333</v>
       </c>
       <c r="B53">
-        <v>12.95138888888889</v>
+        <v>12.951388888888889</v>
       </c>
       <c r="C53">
         <v>14.3</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>334</v>
       </c>
       <c r="B54">
-        <v>13.20138888888889</v>
+        <v>13.201388888888889</v>
       </c>
       <c r="C54">
         <v>14.4</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>335</v>
       </c>
       <c r="B55">
-        <v>13.45138888888889</v>
+        <v>13.451388888888889</v>
       </c>
       <c r="C55">
         <v>14</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>336</v>
       </c>
       <c r="B56">
-        <v>13.70138888888889</v>
+        <v>13.701388888888889</v>
       </c>
       <c r="C56">
         <v>14.3</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>337</v>
       </c>
       <c r="B57">
-        <v>13.95138888888889</v>
+        <v>13.951388888888889</v>
       </c>
       <c r="C57">
         <v>13.8</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>338</v>
       </c>
       <c r="B58">
-        <v>14.20138888888889</v>
+        <v>14.201388888888889</v>
       </c>
       <c r="C58">
         <v>13.7</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>339</v>
       </c>
       <c r="B59">
-        <v>14.45138888888889</v>
+        <v>14.451388888888889</v>
       </c>
       <c r="C59">
         <v>13.9</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>340</v>
       </c>
       <c r="B60">
-        <v>14.70138888888889</v>
+        <v>14.701388888888889</v>
       </c>
       <c r="C60">
         <v>13.7</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>341</v>
       </c>
       <c r="B61">
-        <v>14.95138888888889</v>
+        <v>14.951388888888889</v>
       </c>
       <c r="C61">
         <v>14.6</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>342</v>
       </c>
       <c r="B62">
-        <v>15.20138888888889</v>
+        <v>15.201388888888889</v>
       </c>
       <c r="C62">
         <v>14.1</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>343</v>
       </c>
       <c r="B63">
-        <v>15.45138888888889</v>
+        <v>15.451388888888889</v>
       </c>
       <c r="C63">
         <v>14.2</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>344</v>
       </c>
       <c r="B64">
-        <v>15.70138888888889</v>
+        <v>15.701388888888889</v>
       </c>
       <c r="C64">
         <v>13.8</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>345</v>
       </c>
       <c r="B65">
-        <v>15.95138888888889</v>
+        <v>15.951388888888889</v>
       </c>
       <c r="C65">
         <v>13.6</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>346</v>
       </c>
       <c r="B66">
-        <v>16.20138888888889</v>
+        <v>16.201388888888889</v>
       </c>
       <c r="C66">
         <v>13.8</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>346</v>
       </c>
       <c r="B67">
-        <v>16.20138888888889</v>
+        <v>16.201388888888889</v>
       </c>
       <c r="C67">
         <v>14.6</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>347</v>
       </c>
       <c r="B68">
-        <v>16.45138888888889</v>
+        <v>16.451388888888889</v>
       </c>
       <c r="C68">
         <v>13.6</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>348</v>
       </c>
       <c r="B69">
-        <v>16.70138888888889</v>
+        <v>16.701388888888889</v>
       </c>
       <c r="C69">
         <v>14.2</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>349</v>
       </c>
       <c r="B70">
-        <v>16.95138888888889</v>
+        <v>16.951388888888889</v>
       </c>
       <c r="C70">
         <v>13.7</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>350</v>
       </c>
       <c r="B71">
-        <v>17.20138888888889</v>
+        <v>17.201388888888889</v>
       </c>
       <c r="C71">
         <v>13.8</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>351</v>
       </c>
       <c r="B72">
-        <v>17.45138888888889</v>
+        <v>17.451388888888889</v>
       </c>
       <c r="C72">
         <v>14.4</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>352</v>
       </c>
       <c r="B73">
-        <v>17.70138888888889</v>
+        <v>17.701388888888889</v>
       </c>
       <c r="C73">
         <v>14</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>353</v>
       </c>
       <c r="B74">
-        <v>17.95138888888889</v>
+        <v>17.951388888888889</v>
       </c>
       <c r="C74">
         <v>13.3</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>354</v>
       </c>
       <c r="B75">
-        <v>18.20138888888889</v>
+        <v>18.201388888888889</v>
       </c>
       <c r="C75">
         <v>14.4</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>355</v>
       </c>
       <c r="B76">
-        <v>18.45138888888889</v>
+        <v>18.451388888888889</v>
       </c>
       <c r="C76">
         <v>13.6</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>356</v>
       </c>
       <c r="B77">
-        <v>18.70138888888889</v>
+        <v>18.701388888888889</v>
       </c>
       <c r="C77">
         <v>14.5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>357</v>
       </c>
       <c r="B78">
-        <v>18.95138888888889</v>
+        <v>18.951388888888889</v>
       </c>
       <c r="C78">
         <v>13.4</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C78"/>
+    <ignoredError sqref="A1:C78" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C78"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -3354,7 +3380,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>282</v>
       </c>
@@ -3365,7 +3391,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>283</v>
       </c>
@@ -3376,29 +3402,29 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>284</v>
       </c>
       <c r="B4">
-        <v>0.7013888888888888</v>
+        <v>0.70138888888888884</v>
       </c>
       <c r="C4">
         <v>1086</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>285</v>
       </c>
       <c r="B5">
-        <v>0.9513888888888888</v>
+        <v>0.95138888888888884</v>
       </c>
       <c r="C5">
         <v>1086</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -3409,7 +3435,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -3420,7 +3446,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>288</v>
       </c>
@@ -3431,7 +3457,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>289</v>
       </c>
@@ -3442,777 +3468,779 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>290</v>
       </c>
       <c r="B10">
-        <v>2.201388888888889</v>
+        <v>2.2013888888888888</v>
       </c>
       <c r="C10">
         <v>1079</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>291</v>
       </c>
       <c r="B11">
-        <v>2.451388888888889</v>
+        <v>2.4513888888888888</v>
       </c>
       <c r="C11">
         <v>1076</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>292</v>
       </c>
       <c r="B12">
-        <v>2.701388888888889</v>
+        <v>2.7013888888888888</v>
       </c>
       <c r="C12">
         <v>1072</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>293</v>
       </c>
       <c r="B13">
-        <v>2.951388888888889</v>
+        <v>2.9513888888888888</v>
       </c>
       <c r="C13">
         <v>1068</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>294</v>
       </c>
       <c r="B14">
-        <v>3.201388888888889</v>
+        <v>3.2013888888888888</v>
       </c>
       <c r="C14">
         <v>1066</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>295</v>
       </c>
       <c r="B15">
-        <v>3.451388888888889</v>
+        <v>3.4513888888888888</v>
       </c>
       <c r="C15">
         <v>1062</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>296</v>
       </c>
       <c r="B16">
-        <v>3.701388888888889</v>
+        <v>3.7013888888888888</v>
       </c>
       <c r="C16">
         <v>1057</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>297</v>
       </c>
       <c r="B17">
-        <v>3.951388888888889</v>
+        <v>3.9513888888888888</v>
       </c>
       <c r="C17">
         <v>1055</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>298</v>
       </c>
       <c r="B18">
-        <v>4.201388888888889</v>
+        <v>4.2013888888888893</v>
       </c>
       <c r="C18">
         <v>1051</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>299</v>
       </c>
       <c r="B19">
-        <v>4.451388888888889</v>
+        <v>4.4513888888888893</v>
       </c>
       <c r="C19">
         <v>1047</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>300</v>
       </c>
       <c r="B20">
-        <v>4.701388888888889</v>
+        <v>4.7013888888888893</v>
       </c>
       <c r="C20">
         <v>1044</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>301</v>
       </c>
       <c r="B21">
-        <v>4.951388888888889</v>
+        <v>4.9513888888888893</v>
       </c>
       <c r="C21">
         <v>1042</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>302</v>
       </c>
       <c r="B22">
-        <v>5.201388888888889</v>
+        <v>5.2013888888888893</v>
       </c>
       <c r="C22">
         <v>1041</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>303</v>
       </c>
       <c r="B23">
-        <v>5.451388888888889</v>
+        <v>5.4513888888888893</v>
       </c>
       <c r="C23">
         <v>1037</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>304</v>
       </c>
       <c r="B24">
-        <v>5.701388888888889</v>
+        <v>5.7013888888888893</v>
       </c>
       <c r="C24">
         <v>1033</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>305</v>
       </c>
       <c r="B25">
-        <v>5.951388888888889</v>
+        <v>5.9513888888888893</v>
       </c>
       <c r="C25">
         <v>1031</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>306</v>
       </c>
       <c r="B26">
-        <v>6.201388888888889</v>
+        <v>6.2013888888888893</v>
       </c>
       <c r="C26">
         <v>1020</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>307</v>
       </c>
       <c r="B27">
-        <v>6.451388888888889</v>
+        <v>6.4513888888888893</v>
       </c>
       <c r="C27">
         <v>1027</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>308</v>
       </c>
       <c r="B28">
-        <v>6.701388888888889</v>
+        <v>6.7013888888888893</v>
       </c>
       <c r="C28">
         <v>1025</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>309</v>
       </c>
       <c r="B29">
-        <v>6.951388888888889</v>
+        <v>6.9513888888888893</v>
       </c>
       <c r="C29">
         <v>1024</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>310</v>
       </c>
       <c r="B30">
-        <v>7.201388888888889</v>
+        <v>7.2013888888888893</v>
       </c>
       <c r="C30">
         <v>1022</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>311</v>
       </c>
       <c r="B31">
-        <v>7.451388888888889</v>
+        <v>7.4513888888888893</v>
       </c>
       <c r="C31">
         <v>1020</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>312</v>
       </c>
       <c r="B32">
-        <v>7.701388888888889</v>
+        <v>7.7013888888888893</v>
       </c>
       <c r="C32">
         <v>1018</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>313</v>
       </c>
       <c r="B33">
-        <v>7.951388888888889</v>
+        <v>7.9513888888888893</v>
       </c>
       <c r="C33">
         <v>1017</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>314</v>
       </c>
       <c r="B34">
-        <v>8.20138888888889</v>
+        <v>8.2013888888888893</v>
       </c>
       <c r="C34">
         <v>1016</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>315</v>
       </c>
       <c r="B35">
-        <v>8.45138888888889</v>
+        <v>8.4513888888888893</v>
       </c>
       <c r="C35">
         <v>1014</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>316</v>
       </c>
       <c r="B36">
-        <v>8.70138888888889</v>
+        <v>8.7013888888888893</v>
       </c>
       <c r="C36">
         <v>1014</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>317</v>
       </c>
       <c r="B37">
-        <v>8.95138888888889</v>
+        <v>8.9513888888888893</v>
       </c>
       <c r="C37">
         <v>1013</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>318</v>
       </c>
       <c r="B38">
-        <v>9.20138888888889</v>
+        <v>9.2013888888888893</v>
       </c>
       <c r="C38">
         <v>1013</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>319</v>
       </c>
       <c r="B39">
-        <v>9.45138888888889</v>
+        <v>9.4513888888888893</v>
       </c>
       <c r="C39">
         <v>1010</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>320</v>
       </c>
       <c r="B40">
-        <v>9.70138888888889</v>
+        <v>9.7013888888888893</v>
       </c>
       <c r="C40">
         <v>1010</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>321</v>
       </c>
       <c r="B41">
-        <v>9.95138888888889</v>
+        <v>9.9513888888888893</v>
       </c>
       <c r="C41">
         <v>1008</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>322</v>
       </c>
       <c r="B42">
-        <v>10.20138888888889</v>
+        <v>10.201388888888889</v>
       </c>
       <c r="C42">
         <v>1007</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>323</v>
       </c>
       <c r="B43">
-        <v>10.45138888888889</v>
+        <v>10.451388888888889</v>
       </c>
       <c r="C43">
         <v>1007</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>324</v>
       </c>
       <c r="B44">
-        <v>10.70138888888889</v>
+        <v>10.701388888888889</v>
       </c>
       <c r="C44">
         <v>1006</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>325</v>
       </c>
       <c r="B45">
-        <v>10.95138888888889</v>
+        <v>10.951388888888889</v>
       </c>
       <c r="C45">
         <v>1005</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>326</v>
       </c>
       <c r="B46">
-        <v>11.20138888888889</v>
+        <v>11.201388888888889</v>
       </c>
       <c r="C46">
         <v>1004</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>327</v>
       </c>
       <c r="B47">
-        <v>11.45138888888889</v>
+        <v>11.451388888888889</v>
       </c>
       <c r="C47">
         <v>1004</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>328</v>
       </c>
       <c r="B48">
-        <v>11.70138888888889</v>
+        <v>11.701388888888889</v>
       </c>
       <c r="C48">
         <v>1003</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>329</v>
       </c>
       <c r="B49">
-        <v>11.95138888888889</v>
+        <v>11.951388888888889</v>
       </c>
       <c r="C49">
         <v>1003</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>330</v>
       </c>
       <c r="B50">
-        <v>12.20138888888889</v>
+        <v>12.201388888888889</v>
       </c>
       <c r="C50">
         <v>1002</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>331</v>
       </c>
       <c r="B51">
-        <v>12.45138888888889</v>
+        <v>12.451388888888889</v>
       </c>
       <c r="C51">
         <v>1001</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>332</v>
       </c>
       <c r="B52">
-        <v>12.70138888888889</v>
+        <v>12.701388888888889</v>
       </c>
       <c r="C52">
         <v>1001</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>333</v>
       </c>
       <c r="B53">
-        <v>12.95138888888889</v>
+        <v>12.951388888888889</v>
       </c>
       <c r="C53">
         <v>1000</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>334</v>
       </c>
       <c r="B54">
-        <v>13.20138888888889</v>
+        <v>13.201388888888889</v>
       </c>
       <c r="C54">
         <v>999</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>335</v>
       </c>
       <c r="B55">
-        <v>13.45138888888889</v>
+        <v>13.451388888888889</v>
       </c>
       <c r="C55">
         <v>999</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>336</v>
       </c>
       <c r="B56">
-        <v>13.70138888888889</v>
+        <v>13.701388888888889</v>
       </c>
       <c r="C56">
         <v>998</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>337</v>
       </c>
       <c r="B57">
-        <v>13.95138888888889</v>
+        <v>13.951388888888889</v>
       </c>
       <c r="C57">
         <v>998</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>338</v>
       </c>
       <c r="B58">
-        <v>14.20138888888889</v>
+        <v>14.201388888888889</v>
       </c>
       <c r="C58">
         <v>998</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>339</v>
       </c>
       <c r="B59">
-        <v>14.45138888888889</v>
+        <v>14.451388888888889</v>
       </c>
       <c r="C59">
         <v>998</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>340</v>
       </c>
       <c r="B60">
-        <v>14.70138888888889</v>
+        <v>14.701388888888889</v>
       </c>
       <c r="C60">
         <v>998</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>341</v>
       </c>
       <c r="B61">
-        <v>14.95138888888889</v>
+        <v>14.951388888888889</v>
       </c>
       <c r="C61">
         <v>997</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>342</v>
       </c>
       <c r="B62">
-        <v>15.20138888888889</v>
+        <v>15.201388888888889</v>
       </c>
       <c r="C62">
         <v>996</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>343</v>
       </c>
       <c r="B63">
-        <v>15.45138888888889</v>
+        <v>15.451388888888889</v>
       </c>
       <c r="C63">
         <v>996</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>344</v>
       </c>
       <c r="B64">
-        <v>15.70138888888889</v>
+        <v>15.701388888888889</v>
       </c>
       <c r="C64">
         <v>996</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>345</v>
       </c>
       <c r="B65">
-        <v>15.95138888888889</v>
+        <v>15.951388888888889</v>
       </c>
       <c r="C65">
         <v>995</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>346</v>
       </c>
       <c r="B66">
-        <v>16.20138888888889</v>
+        <v>16.201388888888889</v>
       </c>
       <c r="C66">
         <v>995</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>346</v>
       </c>
       <c r="B67">
-        <v>16.20138888888889</v>
+        <v>16.201388888888889</v>
       </c>
       <c r="C67">
         <v>994</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>347</v>
       </c>
       <c r="B68">
-        <v>16.45138888888889</v>
+        <v>16.451388888888889</v>
       </c>
       <c r="C68">
         <v>995</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>348</v>
       </c>
       <c r="B69">
-        <v>16.70138888888889</v>
+        <v>16.701388888888889</v>
       </c>
       <c r="C69">
         <v>995</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>349</v>
       </c>
       <c r="B70">
-        <v>16.95138888888889</v>
+        <v>16.951388888888889</v>
       </c>
       <c r="C70">
         <v>995</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>350</v>
       </c>
       <c r="B71">
-        <v>17.20138888888889</v>
+        <v>17.201388888888889</v>
       </c>
       <c r="C71">
         <v>994</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>351</v>
       </c>
       <c r="B72">
-        <v>17.45138888888889</v>
+        <v>17.451388888888889</v>
       </c>
       <c r="C72">
         <v>993</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>352</v>
       </c>
       <c r="B73">
-        <v>17.70138888888889</v>
+        <v>17.701388888888889</v>
       </c>
       <c r="C73">
         <v>995</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>353</v>
       </c>
       <c r="B74">
-        <v>17.95138888888889</v>
+        <v>17.951388888888889</v>
       </c>
       <c r="C74">
         <v>995</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>354</v>
       </c>
       <c r="B75">
-        <v>18.20138888888889</v>
+        <v>18.201388888888889</v>
       </c>
       <c r="C75">
         <v>995</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>355</v>
       </c>
       <c r="B76">
-        <v>18.45138888888889</v>
+        <v>18.451388888888889</v>
       </c>
       <c r="C76">
         <v>995</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>356</v>
       </c>
       <c r="B77">
-        <v>18.70138888888889</v>
+        <v>18.701388888888889</v>
       </c>
       <c r="C77">
         <v>995</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>357</v>
       </c>
       <c r="B78">
-        <v>18.95138888888889</v>
+        <v>18.951388888888889</v>
       </c>
       <c r="C78">
         <v>994</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C78"/>
+    <ignoredError sqref="A1:C78" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -4236,17 +4264,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DA2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:105" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -4563,7 +4593,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:105" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -4598,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45373.67361111111</v>
+        <v>45373.673611111109</v>
       </c>
       <c r="M2" t="s">
         <v>136</v>
@@ -4607,7 +4637,7 @@
         <v>137</v>
       </c>
       <c r="O2">
-        <v>45380.67361111111</v>
+        <v>45380.673611111109</v>
       </c>
       <c r="P2" t="s">
         <v>138</v>
@@ -4691,7 +4721,7 @@
         <v>13.4</v>
       </c>
       <c r="AT2">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="AU2">
         <v>0</v>
@@ -4790,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="CA2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="CB2">
         <v>0</v>
@@ -4832,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="CO2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CP2">
         <v>0</v>
@@ -4860,17 +4890,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:DA2"/>
+    <ignoredError sqref="A1:DA2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -4923,7 +4955,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -4952,7 +4984,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9863</v>
       </c>
@@ -4987,7 +5019,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9863</v>
       </c>
@@ -5016,7 +5048,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9863</v>
       </c>
@@ -5030,7 +5062,7 @@
         <v>189</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>185</v>
@@ -5066,7 +5098,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9863</v>
       </c>
@@ -5080,7 +5112,7 @@
         <v>189</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>185</v>
@@ -5116,7 +5148,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9863</v>
       </c>
@@ -5151,7 +5183,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9863</v>
       </c>
@@ -5198,7 +5230,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9863</v>
       </c>
@@ -5227,7 +5259,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9863</v>
       </c>
@@ -5262,7 +5294,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9863</v>
       </c>
@@ -5297,7 +5329,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9863</v>
       </c>
@@ -5333,17 +5365,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5375,7 +5409,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5407,7 +5441,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9863</v>
       </c>
@@ -5439,7 +5473,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9863</v>
       </c>
@@ -5472,27 +5506,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5524,7 +5562,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5557,17 +5595,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5584,7 +5624,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5596,27 +5636,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5666,7 +5710,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5679,8 +5723,8 @@
       <c r="D2">
         <v>6838</v>
       </c>
-      <c r="E2">
-        <v>45373.80134259259</v>
+      <c r="E2" s="1">
+        <v>45373.801342592589</v>
       </c>
       <c r="F2" t="s">
         <v>135</v>
@@ -5710,13 +5754,13 @@
         <v>246</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9863</v>
       </c>
@@ -5729,8 +5773,8 @@
       <c r="D3">
         <v>6838</v>
       </c>
-      <c r="E3">
-        <v>45373.80134259259</v>
+      <c r="E3" s="1">
+        <v>45373.801342592589</v>
       </c>
       <c r="F3" t="s">
         <v>135</v>
@@ -5760,13 +5804,13 @@
         <v>246</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9863</v>
       </c>
@@ -5779,8 +5823,8 @@
       <c r="D4">
         <v>6838</v>
       </c>
-      <c r="E4">
-        <v>45373.80134259259</v>
+      <c r="E4" s="1">
+        <v>45373.801342592589</v>
       </c>
       <c r="F4" t="s">
         <v>135</v>
@@ -5816,7 +5860,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9863</v>
       </c>
@@ -5829,8 +5873,8 @@
       <c r="D5">
         <v>6838</v>
       </c>
-      <c r="E5">
-        <v>45373.80134259259</v>
+      <c r="E5" s="1">
+        <v>45373.801342592589</v>
       </c>
       <c r="F5" t="s">
         <v>135</v>
@@ -5866,7 +5910,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9863</v>
       </c>
@@ -5879,8 +5923,8 @@
       <c r="D6">
         <v>6838</v>
       </c>
-      <c r="E6">
-        <v>45373.80134259259</v>
+      <c r="E6" s="1">
+        <v>45373.801342592589</v>
       </c>
       <c r="F6" t="s">
         <v>135</v>
@@ -5916,7 +5960,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9863</v>
       </c>
@@ -5929,8 +5973,8 @@
       <c r="D7">
         <v>6838</v>
       </c>
-      <c r="E7">
-        <v>45373.80134259259</v>
+      <c r="E7" s="1">
+        <v>45373.801342592589</v>
       </c>
       <c r="F7" t="s">
         <v>135</v>
@@ -5966,7 +6010,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9863</v>
       </c>
@@ -5979,8 +6023,8 @@
       <c r="D8">
         <v>6838</v>
       </c>
-      <c r="E8">
-        <v>45373.80134259259</v>
+      <c r="E8" s="1">
+        <v>45373.801342592589</v>
       </c>
       <c r="F8" t="s">
         <v>135</v>
@@ -6016,7 +6060,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9863</v>
       </c>
@@ -6029,8 +6073,8 @@
       <c r="D9">
         <v>6888</v>
       </c>
-      <c r="E9">
-        <v>45376.65880787037</v>
+      <c r="E9" s="1">
+        <v>45373.658807870372</v>
       </c>
       <c r="F9" t="s">
         <v>135</v>
@@ -6060,13 +6104,13 @@
         <v>246</v>
       </c>
       <c r="O9">
-        <v>7.6041</v>
+        <v>7.6040999999999999</v>
       </c>
       <c r="P9" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9863</v>
       </c>
@@ -6079,8 +6123,8 @@
       <c r="D10">
         <v>6888</v>
       </c>
-      <c r="E10">
-        <v>45376.65880787037</v>
+      <c r="E10" s="1">
+        <v>45373.658807870372</v>
       </c>
       <c r="F10" t="s">
         <v>135</v>
@@ -6116,7 +6160,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9863</v>
       </c>
@@ -6129,8 +6173,8 @@
       <c r="D11">
         <v>6888</v>
       </c>
-      <c r="E11">
-        <v>45376.65880787037</v>
+      <c r="E11" s="1">
+        <v>45373.658807870372</v>
       </c>
       <c r="F11" t="s">
         <v>135</v>
@@ -6166,7 +6210,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9863</v>
       </c>
@@ -6179,8 +6223,8 @@
       <c r="D12">
         <v>6888</v>
       </c>
-      <c r="E12">
-        <v>45376.65880787037</v>
+      <c r="E12" s="1">
+        <v>45373.658807870372</v>
       </c>
       <c r="F12" t="s">
         <v>135</v>
@@ -6216,7 +6260,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9863</v>
       </c>
@@ -6229,8 +6273,8 @@
       <c r="D13">
         <v>6888</v>
       </c>
-      <c r="E13">
-        <v>45376.65880787037</v>
+      <c r="E13" s="1">
+        <v>45373.658807870372</v>
       </c>
       <c r="F13" t="s">
         <v>135</v>
@@ -6266,7 +6310,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9863</v>
       </c>
@@ -6279,8 +6323,8 @@
       <c r="D14">
         <v>6888</v>
       </c>
-      <c r="E14">
-        <v>45376.65880787037</v>
+      <c r="E14" s="1">
+        <v>45373.658807870372</v>
       </c>
       <c r="F14" t="s">
         <v>135</v>
@@ -6316,7 +6360,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9863</v>
       </c>
@@ -6329,8 +6373,8 @@
       <c r="D15">
         <v>6888</v>
       </c>
-      <c r="E15">
-        <v>45376.65880787037</v>
+      <c r="E15" s="1">
+        <v>45373.658807870372</v>
       </c>
       <c r="F15" t="s">
         <v>135</v>
@@ -6366,7 +6410,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9863</v>
       </c>
@@ -6379,7 +6423,7 @@
       <c r="D16">
         <v>7411</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>45391.680763888886</v>
       </c>
       <c r="F16" t="s">
@@ -6416,7 +6460,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9863</v>
       </c>
@@ -6429,8 +6473,8 @@
       <c r="D17">
         <v>7440</v>
       </c>
-      <c r="E17">
-        <v>45392.58716435185</v>
+      <c r="E17" s="1">
+        <v>45392.587164351848</v>
       </c>
       <c r="F17" t="s">
         <v>135</v>
@@ -6466,7 +6510,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9863</v>
       </c>
@@ -6479,8 +6523,8 @@
       <c r="D18">
         <v>7463</v>
       </c>
-      <c r="E18">
-        <v>45392.83938657407</v>
+      <c r="E18" s="1">
+        <v>45392.839386574073</v>
       </c>
       <c r="F18" t="s">
         <v>135</v>
@@ -6510,13 +6554,13 @@
         <v>246</v>
       </c>
       <c r="O18">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="P18" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9863</v>
       </c>
@@ -6529,8 +6573,8 @@
       <c r="D19">
         <v>7512</v>
       </c>
-      <c r="E19">
-        <v>45393.91766203704</v>
+      <c r="E19" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F19" t="s">
         <v>135</v>
@@ -6566,7 +6610,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9863</v>
       </c>
@@ -6579,8 +6623,8 @@
       <c r="D20">
         <v>7512</v>
       </c>
-      <c r="E20">
-        <v>45393.91766203704</v>
+      <c r="E20" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F20" t="s">
         <v>135</v>
@@ -6616,7 +6660,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9863</v>
       </c>
@@ -6629,8 +6673,8 @@
       <c r="D21">
         <v>7512</v>
       </c>
-      <c r="E21">
-        <v>45393.91766203704</v>
+      <c r="E21" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F21" t="s">
         <v>135</v>
@@ -6666,7 +6710,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9863</v>
       </c>
@@ -6679,8 +6723,8 @@
       <c r="D22">
         <v>7512</v>
       </c>
-      <c r="E22">
-        <v>45393.91766203704</v>
+      <c r="E22" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F22" t="s">
         <v>135</v>
@@ -6716,7 +6760,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9863</v>
       </c>
@@ -6729,8 +6773,8 @@
       <c r="D23">
         <v>7512</v>
       </c>
-      <c r="E23">
-        <v>45393.91766203704</v>
+      <c r="E23" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F23" t="s">
         <v>135</v>
@@ -6766,7 +6810,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9863</v>
       </c>
@@ -6779,8 +6823,8 @@
       <c r="D24">
         <v>7512</v>
       </c>
-      <c r="E24">
-        <v>45393.91766203704</v>
+      <c r="E24" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F24" t="s">
         <v>135</v>
@@ -6810,13 +6854,13 @@
         <v>246</v>
       </c>
       <c r="O24">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="P24" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9863</v>
       </c>
@@ -6829,8 +6873,8 @@
       <c r="D25">
         <v>7512</v>
       </c>
-      <c r="E25">
-        <v>45393.91766203704</v>
+      <c r="E25" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F25" t="s">
         <v>135</v>
@@ -6866,7 +6910,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9863</v>
       </c>
@@ -6879,8 +6923,8 @@
       <c r="D26">
         <v>7512</v>
       </c>
-      <c r="E26">
-        <v>45393.91766203704</v>
+      <c r="E26" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F26" t="s">
         <v>135</v>
@@ -6910,13 +6954,13 @@
         <v>246</v>
       </c>
       <c r="O26">
-        <v>0.138</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="P26" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9863</v>
       </c>
@@ -6929,8 +6973,8 @@
       <c r="D27">
         <v>7512</v>
       </c>
-      <c r="E27">
-        <v>45393.91766203704</v>
+      <c r="E27" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F27" t="s">
         <v>135</v>
@@ -6966,7 +7010,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9863</v>
       </c>
@@ -6979,8 +7023,8 @@
       <c r="D28">
         <v>7512</v>
       </c>
-      <c r="E28">
-        <v>45393.91766203704</v>
+      <c r="E28" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F28" t="s">
         <v>135</v>
@@ -7016,7 +7060,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9863</v>
       </c>
@@ -7029,8 +7073,8 @@
       <c r="D29">
         <v>7512</v>
       </c>
-      <c r="E29">
-        <v>45393.91766203704</v>
+      <c r="E29" s="1">
+        <v>45393.917662037042</v>
       </c>
       <c r="F29" t="s">
         <v>135</v>
@@ -7067,8 +7111,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P29"/>
+    <ignoredError sqref="A1:P8 A16:P29 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Datos Experimentales/Data 24027.xlsx
+++ b/Datos Experimentales/Data 24027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A8E003-43DE-4BD4-8A97-3DEB85E1DD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E390CD5E-AAC9-4802-A84E-A15DAD90EC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
@@ -1494,9 +1494,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B118"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1600,7 +1600,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1624,7 +1624,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1696,7 +1696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>91</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>95</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2184,7 +2184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>109</v>
       </c>
@@ -2280,7 +2280,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>111</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2336,7 +2336,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>125</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>127</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>131</v>
       </c>
@@ -2451,7 +2451,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -2463,9 +2463,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>274</v>
       </c>
@@ -2496,9 +2496,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>282</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>283</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>284</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>285</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>288</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>289</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>290</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>291</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>292</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>293</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>294</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>295</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>296</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>297</v>
       </c>
@@ -2685,7 +2685,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>298</v>
       </c>
@@ -2696,7 +2696,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>299</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>300</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>301</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>302</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>303</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>304</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>305</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>306</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>307</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>308</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>309</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>310</v>
       </c>
@@ -2828,7 +2828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>311</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>312</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>313</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>314</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>315</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>316</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>317</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>318</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>319</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>320</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>321</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>322</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>323</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>324</v>
       </c>
@@ -2982,7 +2982,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>325</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>326</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>327</v>
       </c>
@@ -3015,7 +3015,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>328</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>329</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>330</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>331</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>332</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>333</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>334</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>335</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>336</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>337</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>338</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>339</v>
       </c>
@@ -3147,7 +3147,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>340</v>
       </c>
@@ -3158,7 +3158,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>341</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>342</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>343</v>
       </c>
@@ -3191,7 +3191,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>344</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>345</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>346</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>346</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>347</v>
       </c>
@@ -3246,7 +3246,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>348</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>349</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>353</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>354</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>355</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>356</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>357</v>
       </c>
@@ -3367,9 +3367,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>282</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>283</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>284</v>
       </c>
@@ -3413,7 +3413,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>285</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>286</v>
       </c>
@@ -3432,10 +3432,10 @@
         <v>1.2013888888888888</v>
       </c>
       <c r="C6">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>287</v>
       </c>
@@ -3443,10 +3443,10 @@
         <v>1.4513888888888888</v>
       </c>
       <c r="C7">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>288</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>289</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>290</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>291</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>292</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>293</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>294</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>295</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>296</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>297</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>298</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>299</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>300</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>301</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>302</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>303</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>304</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>305</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>306</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>307</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>308</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>309</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>310</v>
       </c>
@@ -3699,7 +3699,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>311</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>312</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>313</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>314</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>315</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>316</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>317</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>318</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>319</v>
       </c>
@@ -3798,7 +3798,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>320</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>321</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>322</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>323</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>324</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>325</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>326</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>327</v>
       </c>
@@ -3886,7 +3886,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>328</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>329</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>330</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>331</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>332</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>333</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>334</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>335</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>336</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>337</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>338</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>339</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>340</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>341</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>342</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>343</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>344</v>
       </c>
@@ -4073,7 +4073,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>345</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>346</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>346</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>347</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>348</v>
       </c>
@@ -4128,7 +4128,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>349</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>350</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -4161,7 +4161,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>352</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>353</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>354</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>355</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>356</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>357</v>
       </c>
@@ -4230,7 +4230,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C78" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C5 A8:C78 A6:B6 A7:B7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4238,9 +4238,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -4274,9 +4274,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DA2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:105" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:105" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:105" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -4900,9 +4900,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -4955,7 +4955,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9863</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9863</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9863</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9863</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>136</v>
       </c>
       <c r="L6">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="M6" t="s">
         <v>5</v>
@@ -5148,7 +5148,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9863</v>
       </c>
@@ -5183,7 +5183,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9863</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9863</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9863</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9863</v>
       </c>
@@ -5329,7 +5329,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9863</v>
       </c>
@@ -5367,7 +5367,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:Q5 A7:Q12 A6:K6 M6:Q6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5375,9 +5375,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5441,7 +5441,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9863</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>217</v>
       </c>
       <c r="H3">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="I3">
         <v>45373</v>
@@ -5473,7 +5473,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9863</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>215</v>
       </c>
       <c r="H4">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="I4">
         <v>45373</v>
@@ -5508,7 +5508,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J2 A4:G4 A3:G3 I3:J3 I4:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5516,7 +5516,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -5528,9 +5528,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5605,9 +5605,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5624,7 +5624,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5646,7 +5646,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -5658,9 +5658,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>164</v>
       </c>
@@ -5710,7 +5710,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9863</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9863</v>
       </c>
@@ -5810,7 +5810,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9863</v>
       </c>
@@ -5860,7 +5860,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9863</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9863</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9863</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9863</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9863</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9863</v>
       </c>
@@ -6160,7 +6160,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9863</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9863</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9863</v>
       </c>
@@ -6310,7 +6310,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9863</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9863</v>
       </c>
@@ -6410,7 +6410,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9863</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9863</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9863</v>
       </c>
@@ -6560,7 +6560,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9863</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9863</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9863</v>
       </c>
@@ -6710,7 +6710,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9863</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9863</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9863</v>
       </c>
@@ -6860,7 +6860,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9863</v>
       </c>
@@ -6910,7 +6910,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9863</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9863</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9863</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9863</v>
       </c>
